--- a/artfynd/A 20639-2026 artfynd.xlsx
+++ b/artfynd/A 20639-2026 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>180900</v>
       </c>
       <c r="B2" t="n">
-        <v>104450</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542834.4320992207</v>
+        <v>542834</v>
       </c>
       <c r="R2" t="n">
-        <v>6295867.790633705</v>
+        <v>6295868</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -762,19 +757,9 @@
           <t>2008-08-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-08-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -818,16 +803,11 @@
         <v>723439</v>
       </c>
       <c r="B3" t="n">
-        <v>101201</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -864,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542848.0559849543</v>
+        <v>542848</v>
       </c>
       <c r="R3" t="n">
-        <v>6295876.690191383</v>
+        <v>6295877</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -892,24 +872,19 @@
           <t>Hälleberga</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Arkiv-Hf-Nyb-0164</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2010-07-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2010-07-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,7 +914,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 20639-2026 artfynd.xlsx
+++ b/artfynd/A 20639-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/180900</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -917,8 +927,17 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/723439</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>